--- a/templates/student-engagement-dashboard-starter.xlsx
+++ b/templates/student-engagement-dashboard-starter.xlsx
@@ -8,33 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\Project Files\Github\student-engagement\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDCE47E-A796-4CE6-9BA0-D05A1B1865F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFAD3B4-AFF1-4C0C-8960-8F200BE9DCA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="_PivotHost" sheetId="8" state="veryHidden" r:id="rId1"/>
+    <sheet name="_PivotHost" sheetId="9" state="veryHidden" r:id="rId1"/>
     <sheet name="How to use" sheetId="1" r:id="rId2"/>
     <sheet name="Dashboard" sheetId="2" r:id="rId3"/>
     <sheet name="Visitor" sheetId="3" r:id="rId4"/>
     <sheet name="Outreach" sheetId="4" r:id="rId5"/>
-    <sheet name="Reports — Weekly" sheetId="5" r:id="rId6"/>
-    <sheet name="Reports — Monthly" sheetId="6" r:id="rId7"/>
-    <sheet name="_Helpers" sheetId="7" state="hidden" r:id="rId8"/>
+    <sheet name="VisitorLong" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet name="Reports — Weekly" sheetId="6" r:id="rId7"/>
+    <sheet name="Reports — Monthly" sheetId="7" r:id="rId8"/>
+    <sheet name="_Helpers" sheetId="8" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="Slicer_Campus">#N/A</definedName>
-    <definedName name="Slicer_Time_block">#N/A</definedName>
+    <definedName name="Slicer_Time_block_this_submission_covers">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId9"/>
+    <pivotCache cacheId="7" r:id="rId10"/>
+    <pivotCache cacheId="11" r:id="rId11"/>
+    <pivotCache cacheId="17" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId10"/>
-        <x14:slicerCache r:id="rId11"/>
+        <x14:slicerCache r:id="rId13"/>
+        <x14:slicerCache r:id="rId14"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -56,96 +59,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="116">
-  <si>
-    <t>How to use this workbook</t>
-  </si>
-  <si>
-    <t>This is the Option A+ starter — it's pre-built with the data tables, KPI tiles, heatmap, and three charts. You need to do two things to make it live: connect Power Query to your Forms response files, and (optionally) add slicers / a timeline for interactive filtering.</t>
-  </si>
-  <si>
-    <t>Sheet by sheet</t>
-  </si>
-  <si>
-    <t>• Dashboard — Shannon's main view. KPI tiles, Campus × Time block heatmap, top categories chart, outreach themes chart, outreach by campus chart. All sourced from formulas — no pivots needed.</t>
-  </si>
-  <si>
-    <t>• Visitor — empty data table with all 32 columns matching the Forms export. Power Query will load Forms responses here.</t>
-  </si>
-  <si>
-    <t>• Outreach — empty data table with 10 columns. Same as above, for outreach.</t>
-  </si>
-  <si>
-    <t>• _Helpers — hidden sheet with the small helper tables that drive the charts. Don't delete.</t>
-  </si>
-  <si>
-    <t>Step 1 — Connect Power Query (one-time, ~10 min)</t>
-  </si>
-  <si>
-    <t>Open each form in forms.office.com → Responses → Open in Excel. Microsoft creates an auto-syncing workbook in your OneDrive. Save those files in OneDrive/Student Engagement/Live Data/.</t>
-  </si>
-  <si>
-    <t>Then in this workbook: Data → Get Data → From File → From Workbook → pick the Visitor responses file → Sheet1 → Transform Data. Replace nulls with 0 in the 24 category columns. Close &amp; Load To... → Existing worksheet → cell A1 of the Visitor sheet.</t>
-  </si>
-  <si>
-    <t>Repeat for the Outreach responses file → load into the Outreach sheet.</t>
-  </si>
-  <si>
-    <t>Data → Queries &amp; Connections → right-click each query → Properties → tick 'Refresh data when opening the file' AND 'Refresh every 5 minutes'.</t>
-  </si>
-  <si>
-    <t>That's it. The dashboard now updates within a minute of every new submission.</t>
-  </si>
-  <si>
-    <t>Step 2 — Optional polish</t>
-  </si>
-  <si>
-    <t>Add slicers and a timeline for interactive filtering: Insert a PivotTable on tblVisitor (any pivot, even a hidden one), then Insert → Slicer (tick Campus, Time block) and Insert → Timeline (tick Submitted at). Connect the slicers to all charts via Slicer → Report Connections. The dashboard becomes click-to-filter.</t>
-  </si>
-  <si>
-    <t>Add a daily trend line chart: Insert PivotChart on tblVisitor → Date axis = Submitted at (grouped by days), value = Sum of How many helped. Drop the chart on the Dashboard sheet.</t>
-  </si>
-  <si>
-    <t>Add a section-mix stacked bar: same idea, with Campus on the row axis and a custom Section-bucket column on the column axis.</t>
-  </si>
-  <si>
-    <t>Daily refresh</t>
-  </si>
-  <si>
-    <t>• Open the file. Data refreshes automatically within ~30 seconds.</t>
-  </si>
-  <si>
-    <t>• If you want to force a refresh: Data → Refresh All (or Ctrl+Alt+F5).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="96">
+  <si>
+    <t>How to use this workbook (v2 — long-format)</t>
+  </si>
+  <si>
+    <t>This template is built around the actual Microsoft Forms export shape, with category data unpivoted into a long-format table so adding a new question in Forms doesn't break anything.</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>• Dashboard — Shannon's main view. KPI tiles, heatmap, slicers, charts.</t>
+  </si>
+  <si>
+    <t>• Visitor — wide table tblVisitor (one row per submission). Columns match Forms export exactly.</t>
+  </si>
+  <si>
+    <t>• Outreach — wide table tblOutreach. Same.</t>
+  </si>
+  <si>
+    <t>• Reports — Weekly / Monthly — pre-built pivots grouped by date. Filtered by the Dashboard slicers.</t>
+  </si>
+  <si>
+    <t>• VisitorLong (hidden) — long-format table tblVisitorLong with one row per (submission × category). Auto-handles new categories.</t>
+  </si>
+  <si>
+    <t>• _Helpers (hidden) — small helper formulas the Top Campus KPI uses.</t>
+  </si>
+  <si>
+    <t>• _PivotHost (hidden, added by post-build) — owns the slicer-source pivot.</t>
+  </si>
+  <si>
+    <t>Power Query setup — three queries</t>
+  </si>
+  <si>
+    <t>On first use, after saving this template into OneDrive:</t>
+  </si>
+  <si>
+    <t>(1) Visitor query — Data → Get Data → From File → From Workbook → pick your Visitor responses .xlsx → Sheet1 → Close &amp; Load To... → Existing worksheet → A1 of Visitor sheet → click Replace when Excel asks → table named tblVisitor.</t>
+  </si>
+  <si>
+    <t>(2) Outreach query — same as Visitor, but pick your Outreach responses .xlsx and load to A1 of Outreach sheet → table named tblOutreach.</t>
+  </si>
+  <si>
+    <t>(3) VisitorLong query — Right-click the Visitor query in the Queries &amp; Connections panel → Reference. New query opens. Rename to VisitorLong. Select the 24 category columns (Wayfinding through Others; NOT Others (Inquiry)). Right-click selected → Unpivot Columns. Rename Attribute → Category and Value → Count. Close &amp; Load To... → Existing worksheet → A1 of VisitorLong sheet (it's hidden — unhide briefly via right-click any tab → Unhide → VisitorLong). Replace tblVisitorLong when prompted. Re-hide.</t>
+  </si>
+  <si>
+    <t>(4) Set all 3 queries to refresh on open + every 5 minutes: Data → Queries &amp; Connections → right-click each query → Properties → tick both checkboxes.</t>
+  </si>
+  <si>
+    <t>Why this is future-proof</t>
+  </si>
+  <si>
+    <t>• Adding a new category in Forms (e.g., 'Voter Registration'): Power Query loads it as a new column on tblVisitor. The next refresh of the VisitorLong query auto-includes it via Unpivot Columns. The Top Categories chart and Inquiries Logged KPI both pull from tblVisitorLong, so the new category appears with zero formula edits.</t>
+  </si>
+  <si>
+    <t>• Renaming a question in Forms: Power Query throws on next refresh because it expects the old column name. Edit the query → 'Renamed Columns' step → update the mapping. ~30 seconds.</t>
+  </si>
+  <si>
+    <t>• Adding a new campus: appears automatically in slicers and pivots. Update the helper table on _Helpers (rows 4-7) for the Top Campus KPI.</t>
   </si>
   <si>
     <t>If something looks broken</t>
   </si>
   <si>
-    <t>• KPI shows #REF! → the table reference is broken. Click the cell to see which table/column it's looking for. Most likely the table got renamed; restore tblVisitor / tblOutreach as the table names (Table Design tab).</t>
-  </si>
-  <si>
-    <t>• KPI shows 0 when you expect numbers → check Data → Queries &amp; Connections; the Forms responses file may have moved. Edit the query → fix the source path.</t>
-  </si>
-  <si>
-    <t>• Heatmap is all empty → the Time block question wording must match TIME_BLOCKS exactly: 'Morning (open – 12pm)', 'Afternoon (12 – 4pm)', 'Evening (4pm – close)'. Em-dashes matter; check carefully.</t>
-  </si>
-  <si>
-    <t>Maintenance</t>
-  </si>
-  <si>
-    <t>• Adding a category in Forms → after the next submission, the new column appears in the Forms export. Power Query refresh picks it up. To include it in the 'Inquiries logged' KPI, edit that formula on the Dashboard sheet.</t>
-  </si>
-  <si>
-    <t>• Renaming a Forms question → Power Query will throw on next refresh because it expects the old column name. Edit the query → 'Renamed Columns' step → update the mapping.</t>
-  </si>
-  <si>
-    <t>• Adding a new campus → update the helper table on _Helpers (rows 4-7) and the heatmap rows on the Dashboard.</t>
+    <t>• KPI shows #REF! → a column reference is broken. Click the cell to see which column it's looking for, then check that column exists in your data with that exact name.</t>
+  </si>
+  <si>
+    <t>• Heatmap is all zeros even with data → the Time block question wording must START with 'Morning' / 'Afternoon' / 'Evening'. Heatmap formulas use wildcard matching to be resilient, but if your Time block options start with different words, update the heatmap formulas on Dashboard rows 9-12.</t>
+  </si>
+  <si>
+    <t>• Slicers don't filter the Top Categories or Outreach charts → expected. Those charts source from different tables (tblVisitorLong, tblOutreach), so they always show lifetime totals. The slicers/timeline filter only the heatmap-source pivot and the Reports sheets.</t>
   </si>
   <si>
     <t>Student Engagement Dashboard</t>
   </si>
   <si>
-    <t>Sums every submission in tblVisitor / tblOutreach. Add a date timeline + slicers later for interactive filtering.</t>
+    <t>Lifetime KPIs and heatmap. Slicers/timeline filter the Reports — Weekly / Monthly sheets.</t>
   </si>
   <si>
     <t xml:space="preserve">  KEY METRICS</t>
@@ -163,7 +154,7 @@
     <t>PEOPLE HELPED (OUTREACH)</t>
   </si>
   <si>
-    <t>Sum across all 24 categories</t>
+    <t>Sum across all categories (auto-includes new ones)</t>
   </si>
   <si>
     <t xml:space="preserve">  ENGAGEMENT HEATMAP — CAMPUS × TIME BLOCK</t>
@@ -193,10 +184,7 @@
     <t>Cambridge</t>
   </si>
   <si>
-    <t xml:space="preserve">  TOP INQUIRY CATEGORIES</t>
-  </si>
-  <si>
-    <t>Chart sourced from _Helpers!H column. Sort the helper rows by count desc to manually rank the bars.</t>
+    <t xml:space="preserve">  TOP INQUIRY CATEGORIES — auto-populated from tblVisitorLong</t>
   </si>
   <si>
     <t xml:space="preserve">  OUTREACH THEMES — PEOPLE HELPED</t>
@@ -205,34 +193,34 @@
     <t xml:space="preserve">  OUTREACH REACH BY CAMPUS</t>
   </si>
   <si>
-    <t xml:space="preserve">  WHAT'S MISSING — ADD MANUALLY IN EXCEL</t>
-  </si>
-  <si>
-    <t>The starter pre-builds: data tables, KPI tiles, heatmap, and 3 charts.</t>
-  </si>
-  <si>
-    <t>Add manually for full interactivity: 1) Power Query connection to your Forms response files (Data → Get Data → From File → From Workbook). 2) Slicers on Campus/Time block (Insert → Slicer, after creating any pivot table). 3) Date Timeline (Insert → Timeline). See excel-dashboard-build-guide.md for the rest.</t>
-  </si>
-  <si>
-    <t>Submission ID</t>
-  </si>
-  <si>
-    <t>Submitted at</t>
+    <t xml:space="preserve">  WHAT'S NEXT</t>
+  </si>
+  <si>
+    <t>1) Connect Power Query (3 queries: Visitor, VisitorLong, Outreach). 2) Run scripts/post-build.py to add slicers + report pivots + charts. 3) Add a Timeline manually after data flows in. See excel-dashboard-build-guide.md.</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Start time</t>
+  </si>
+  <si>
+    <t>Completion time</t>
+  </si>
+  <si>
+    <t>Email</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Time block</t>
-  </si>
-  <si>
-    <t>How many helped</t>
-  </si>
-  <si>
-    <t>Wayfinding – General</t>
+    <t>Time block this submission covers</t>
+  </si>
+  <si>
+    <t>How many people did you help during this time block?</t>
+  </si>
+  <si>
+    <t>Wayfinding</t>
   </si>
   <si>
     <t>OneCard</t>
@@ -283,22 +271,22 @@
     <t>International Transition Services</t>
   </si>
   <si>
-    <t>International Admissions – Second Program</t>
-  </si>
-  <si>
-    <t>Library – Tech Loans / TeachMeTech</t>
-  </si>
-  <si>
-    <t>Library – Research / Writing Consultants</t>
-  </si>
-  <si>
-    <t>Library – Academic Integrity</t>
-  </si>
-  <si>
-    <t>CSI – Frosh Kits</t>
-  </si>
-  <si>
-    <t>CSI – Peer Advocates</t>
+    <t>International Admissions - Second Program</t>
+  </si>
+  <si>
+    <t>Library - Tech Loans / TeachMeTech</t>
+  </si>
+  <si>
+    <t>Library - Research / Writing Consultants</t>
+  </si>
+  <si>
+    <t>Library - Academic Integrity</t>
+  </si>
+  <si>
+    <t>CSI - Frosh Kits</t>
+  </si>
+  <si>
+    <t>CSI - Peer Advocates</t>
   </si>
   <si>
     <t>Others</t>
@@ -307,93 +295,42 @@
     <t>Others (Inquiry)</t>
   </si>
   <si>
-    <t>Date of activity</t>
+    <t>Date of outreach activity</t>
+  </si>
+  <si>
+    <t>How many people attended the outreach activity?</t>
   </si>
   <si>
     <t>Outreach Activity</t>
   </si>
   <si>
-    <t>Other activity (text)</t>
-  </si>
-  <si>
-    <t>Notes</t>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>(placeholder)</t>
   </si>
   <si>
     <t>Weekly Report</t>
   </si>
   <si>
-    <t>This sheet is a placeholder for the rolled-up report. To build it: Insert a PivotTable on tblVisitor → Rows: Submitted at (right-click → Group → Days × 7 + Months + Years), Campus → Values: Sum of How many helped. Drop slicers for Campus and Time block. Print Layout → Landscape, Page Setup → Print Area = the pivot range. Page → File → Export → PDF.</t>
+    <t>PivotTable below is built by post-build.py. After data loads, right-click any date → Group → tick Days (7) + Months + Years for proper rollup.</t>
   </si>
   <si>
     <t>Monthly Report</t>
   </si>
   <si>
-    <t>This sheet is a placeholder for the rolled-up report. To build it: Insert a PivotTable on tblVisitor → Rows: Submitted at (right-click → Group → Months + Years), Campus → Values: Sum of How many helped. Drop slicers for Campus and Time block. Print Layout → Landscape, Page Setup → Print Area = the pivot range. Page → File → Export → PDF.</t>
+    <t>PivotTable below is built by post-build.py. After data loads, right-click any date → Group → tick Months + Years for proper rollup.</t>
   </si>
   <si>
     <t>CAMPUS TOTALS</t>
   </si>
   <si>
-    <t>DAILY TOTALS (helper)</t>
-  </si>
-  <si>
-    <t>CATEGORY TOTALS</t>
-  </si>
-  <si>
-    <t>OUTREACH THEME TOTALS</t>
-  </si>
-  <si>
-    <t>OUTREACH BY CAMPUS</t>
-  </si>
-  <si>
     <t>People helped</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Total inquiries</t>
-  </si>
-  <si>
-    <t>Theme</t>
-  </si>
-  <si>
-    <t>(Build a PivotChart on tblVisitor for the daily trend — too dynamic for a static helper.)</t>
-  </si>
-  <si>
-    <t>Bell Let's Talk</t>
-  </si>
-  <si>
-    <t>Black History Month</t>
-  </si>
-  <si>
-    <t>Campus Welcome Day</t>
-  </si>
-  <si>
-    <t>CCR and SSP Promotion</t>
-  </si>
-  <si>
-    <t>Celebrating Diversity</t>
-  </si>
-  <si>
-    <t>Health and Wellness Outreach</t>
-  </si>
-  <si>
-    <t>International Women's Day</t>
-  </si>
-  <si>
-    <t>Pride Month</t>
-  </si>
-  <si>
-    <t>Sexual Health Week</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>Row Labels</t>
   </si>
   <si>
@@ -403,7 +340,13 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Sum of How many helped</t>
+    <t>Sum of How many people did you help during this time block?</t>
+  </si>
+  <si>
+    <t>Sum of Count</t>
+  </si>
+  <si>
+    <t>Sum of How many people attended the outreach activity?</t>
   </si>
 </sst>
 </file>
@@ -435,15 +378,15 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF024C4F"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF707070"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF024C4F"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -557,9 +500,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -580,7 +523,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -588,11 +530,10 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -600,11 +541,12 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -635,192 +577,127 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[student-engagement-dashboard-starter.xlsx]_PivotHost!ptTopCategories</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>_Helpers!$H$3</c:f>
+              <c:f>_PivotHost!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total inquiries</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
             <a:ln>
-              <a:prstDash val="solid"/>
+              <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>_Helpers!$G$4:$G$27</c:f>
+              <c:f>_PivotHost!$D$2:$D$3</c:f>
               <c:strCache>
-                <c:ptCount val="24"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Wayfinding – General</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>OneCard</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>IT Support</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Bus Pass / Transportation</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Parking</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Timetable / Registration Concern</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Student Fees / Student Financial Services</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Learning Services / Math Help / Tutors</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Want to Change Program</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Connect with Faculty / Program Coordinator / Chair</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Health Insurance</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Mental Health Support / Counselling</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Medical Clinic / Medical Care</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Housing / Accommodation</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Job Search / Career Services</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Immigration / International Student Advising Referral</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>International Transition Services</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>International Admissions – Second Program</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Library – Tech Loans / TeachMeTech</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Library – Research / Writing Consultants</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Library – Academic Integrity</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>CSI – Frosh Kits</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>CSI – Peer Advocates</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Others</c:v>
+                  <c:v>(placeholder)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>_Helpers!$H$4:$H$27</c:f>
+              <c:f>_PivotHost!$E$2:$E$3</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="24"/>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="23">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -828,7 +705,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC0A-4B6B-BEB9-6E545B097220}"/>
+              <c16:uniqueId val="{0000000B-B30B-4A8A-9296-1D384DB80283}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -840,54 +717,182 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="972983744"/>
+        <c:axId val="972991904"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10"/>
+        <c:axId val="972983744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="972991904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="100"/>
+        <c:axId val="972991904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="972983744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
 </c:chartSpace>
 </file>
 
@@ -895,108 +900,127 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[student-engagement-dashboard-starter.xlsx]_PivotHost!ptOutreachThemes</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>_Helpers!$K$3</c:f>
+              <c:f>_PivotHost!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>People helped</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
             <a:ln>
-              <a:prstDash val="solid"/>
+              <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>_Helpers!$J$4:$J$13</c:f>
+              <c:f>_PivotHost!$G$2:$G$3</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bell Let's Talk</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Black History Month</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Campus Welcome Day</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>CCR and SSP Promotion</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Celebrating Diversity</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Health and Wellness Outreach</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>International Women's Day</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Pride Month</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Sexual Health Week</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other</c:v>
+                  <c:v>(blank)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>_Helpers!$K$4:$K$13</c:f>
+              <c:f>_PivotHost!$H$2:$H$3</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1004,7 +1028,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BCF4-4A10-A4A4-75489EE06753}"/>
+              <c16:uniqueId val="{0000000B-0D59-4E75-BC65-27D4494E809F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1016,54 +1040,182 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="972990944"/>
+        <c:axId val="972982784"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10"/>
+        <c:axId val="972990944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="972982784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="100"/>
+        <c:axId val="972982784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="972990944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
 </c:chartSpace>
 </file>
 
@@ -1071,72 +1223,127 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="2"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[student-engagement-dashboard-starter.xlsx]_PivotHost!ptOutreachByCampus</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>_Helpers!$N$3</c:f>
+              <c:f>_PivotHost!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>People helped</c:v>
+                  <c:v>Total</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
             <a:ln>
-              <a:prstDash val="solid"/>
+              <a:noFill/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="1"/>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>_Helpers!$M$4:$M$7</c:f>
+              <c:f>_PivotHost!$J$2:$J$3</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Waterloo</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Doon</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Reuter</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Cambridge</c:v>
+                  <c:v>(blank)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>_Helpers!$N$4:$N$7</c:f>
+              <c:f>_PivotHost!$K$2:$K$3</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1144,7 +1351,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-991E-477A-9F79-A7068D049BF2}"/>
+              <c16:uniqueId val="{0000000B-8803-411D-B9B3-319CFC2A5D2C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1156,152 +1363,1816 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="972978944"/>
+        <c:axId val="972992864"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10"/>
+        <c:axId val="972978944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="972992864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="100"/>
+        <c:axId val="972992864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="972978944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6480000" cy="4320000"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6480000" cy="3960000"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="6480000" cy="2880000"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1319,10 +3190,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="5" name="slCampus">
+            <xdr:cNvPr id="2" name="slCampus">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{347B9A6D-7EBF-C079-5F35-05CC31613800}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D600BEC0-61F6-F70E-A26D-B85C9235F9EB}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1389,7 +3260,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
+      <xdr:colOff>635000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>65087</xdr:rowOff>
     </xdr:to>
@@ -1397,10 +3268,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="slTime">
+            <xdr:cNvPr id="3" name="slTime">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD78426E-CEB7-C3E2-AD2B-9F8D57D92790}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C95D746-F290-0B59-E45C-8E8942C676A9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1428,7 +3299,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="2921000" y="381000"/>
-              <a:ext cx="3302000" cy="1651000"/>
+              <a:ext cx="3429000" cy="1651000"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1458,29 +3329,140 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>223837</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="chTopCategories">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B5FF3B-C1E9-9946-ACC0-C0E1A1EDF5E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="chOutreachThemes">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D69364F0-CCEB-3CB5-5E59-87627B001B7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>163512</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>169862</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="chOutreachByCampus">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6800CA24-29A9-963E-E506-F7D706396A3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.720999652774" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{A24F83AB-48C8-4561-A822-0D979324B70B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.820775231485" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{487A8BB3-6719-4684-A36E-D58B084C6269}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblVisitor"/>
   </cacheSource>
-  <cacheFields count="32">
-    <cacheField name="Submission ID" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+  <cacheFields count="33">
+    <cacheField name="Id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="3"/>
     </cacheField>
-    <cacheField name="Submitted at" numFmtId="165">
+    <cacheField name="Start time" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2025-01-01T00:00:00"/>
+    </cacheField>
+    <cacheField name="Completion time" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2025-01-01T00:00:00" count="3">
         <d v="2024-01-01T00:00:00"/>
         <d v="2024-06-15T00:00:00"/>
         <d v="2024-12-31T00:00:00"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Name" numFmtId="0">
+    <cacheField name="Email" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Email" numFmtId="0">
+    <cacheField name="Name" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Campus" numFmtId="0">
@@ -1488,15 +3470,15 @@
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Time block" numFmtId="0">
+    <cacheField name="Time block this submission covers" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="How many helped" numFmtId="0">
+    <cacheField name="How many people did you help during this time block?" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
-    <cacheField name="Wayfinding – General" numFmtId="0">
+    <cacheField name="Wayfinding" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="OneCard" numFmtId="0">
@@ -1547,22 +3529,22 @@
     <cacheField name="International Transition Services" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
-    <cacheField name="International Admissions – Second Program" numFmtId="0">
+    <cacheField name="International Admissions - Second Program" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
-    <cacheField name="Library – Tech Loans / TeachMeTech" numFmtId="0">
+    <cacheField name="Library - Tech Loans / TeachMeTech" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
-    <cacheField name="Library – Research / Writing Consultants" numFmtId="0">
+    <cacheField name="Library - Research / Writing Consultants" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
-    <cacheField name="Library – Academic Integrity" numFmtId="0">
+    <cacheField name="Library - Academic Integrity" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
-    <cacheField name="CSI – Frosh Kits" numFmtId="0">
+    <cacheField name="CSI - Frosh Kits" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
-    <cacheField name="CSI – Peer Advocates" numFmtId="0">
+    <cacheField name="CSI - Peer Advocates" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
     </cacheField>
     <cacheField name="Others" numFmtId="0">
@@ -1574,7 +3556,94 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="957050663"/>
+      <x14:pivotCacheDefinition pivotCacheId="1083663819"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.820779166665" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{29FDED5C-D45E-410C-A1AF-024DD98828B8}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="tblVisitorLong"/>
+  </cacheSource>
+  <cacheFields count="8">
+    <cacheField name="Id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="3"/>
+    </cacheField>
+    <cacheField name="Completion time" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2025-01-01T00:00:00"/>
+    </cacheField>
+    <cacheField name="Email" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Campus" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Time block this submission covers" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Category" numFmtId="0">
+      <sharedItems count="1">
+        <s v="(placeholder)"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Count" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.820788888886" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{BCDBE610-5152-4118-B353-CCCC8F7BCE83}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="tblOutreach"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Id" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="3"/>
+    </cacheField>
+    <cacheField name="Start time" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2025-01-01T00:00:00"/>
+    </cacheField>
+    <cacheField name="Completion time" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2025-01-01T00:00:00"/>
+    </cacheField>
+    <cacheField name="Email" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Campus" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Date of outreach activity" numFmtId="166">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-01-01T00:00:00" maxDate="2025-01-01T00:00:00"/>
+    </cacheField>
+    <cacheField name="How many people attended the outreach activity?" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+    </cacheField>
+    <cacheField name="Outreach Activity" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1" count="1">
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -1583,7 +3652,8 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="3">
   <r>
-    <m/>
+    <n v="1"/>
+    <d v="2024-01-01T00:00:00"/>
     <x v="0"/>
     <m/>
     <m/>
@@ -1617,7 +3687,8 @@
     <m/>
   </r>
   <r>
-    <m/>
+    <n v="2"/>
+    <d v="2024-06-15T00:00:00"/>
     <x v="1"/>
     <m/>
     <m/>
@@ -1651,7 +3722,8 @@
     <m/>
   </r>
   <r>
-    <m/>
+    <n v="3"/>
+    <d v="2024-12-31T00:00:00"/>
     <x v="2"/>
     <m/>
     <m/>
@@ -1687,11 +3759,261 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="3">
+  <r>
+    <n v="1"/>
+    <d v="2024-01-01T00:00:00"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <d v="2024-06-15T00:00:00"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <d v="2024-12-31T00:00:00"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <n v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="3">
+  <r>
+    <n v="1"/>
+    <d v="2024-01-01T00:00:00"/>
+    <d v="2024-01-01T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <d v="2024-01-01T00:00:00"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <d v="2024-06-15T00:00:00"/>
+    <d v="2024-06-15T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <d v="2024-06-15T00:00:00"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <d v="2024-12-31T00:00:00"/>
+    <d v="2024-12-31T00:00:00"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <d v="2024-12-31T00:00:00"/>
+    <n v="0"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00E61731-6C31-400D-B992-5CE3D855CE93}" name="ptSlicerHost" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{16C8CC98-62E0-4963-817E-18A684A81D2E}" name="ptOutreachByCampus" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="J1:K3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of How many people attended the outreach activity?" fld="7" baseField="0" baseItem="0" numFmtId="1"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7E51020-C0DC-4E0E-BC9C-98DFD9107402}" name="ptOutreachThemes" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="G1:H3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="8"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of How many people attended the outreach activity?" fld="7" baseField="0" baseItem="0" numFmtId="1"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EAA0FC79-74EC-462F-8883-BC857E166A82}" name="ptTopCategories" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Count" fld="7" baseField="0" baseItem="0" numFmtId="1"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BC194E73-8C73-4EA3-BE42-A5387AD0CDAA}" name="ptSlicerHost" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -1735,7 +4057,7 @@
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="4"/>
+    <field x="5"/>
   </rowFields>
   <rowItems count="2">
     <i>
@@ -1749,7 +4071,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of How many helped" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Sum of How many people did you help during this time block?" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1763,11 +4085,12 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61B6C28F-8548-4152-94D7-8A15AAFBDB44}" name="ptWeekly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B3D2BBFF-1ED6-44F6-AF36-6A915727236E}" name="ptWeekly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B10:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" numFmtId="165" outline="0" showAll="0">
       <items count="4">
         <item x="0"/>
@@ -1818,7 +4141,7 @@
     <pivotField compact="0" outline="0" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="2"/>
   </rowFields>
   <rowItems count="4">
     <i>
@@ -1835,7 +4158,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="4"/>
+    <field x="5"/>
   </colFields>
   <colItems count="2">
     <i>
@@ -1846,7 +4169,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of How many helped" fld="6" baseField="0" baseItem="0" numFmtId="1"/>
+    <dataField name="Sum of How many people did you help during this time block?" fld="7" baseField="0" baseItem="0" numFmtId="1"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1860,11 +4183,12 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78538331-B5E7-462A-980F-5AB765A45B8D}" name="ptMonthly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1519812-928F-49FB-9BB8-9A18DC4B6F78}" name="ptMonthly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B10:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="165" outline="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" numFmtId="165" outline="0" showAll="0">
       <items count="4">
         <item x="0"/>
@@ -1915,7 +4239,7 @@
     <pivotField compact="0" outline="0" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="2"/>
   </rowFields>
   <rowItems count="4">
     <i>
@@ -1932,7 +4256,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="4"/>
+    <field x="5"/>
   </colFields>
   <colItems count="2">
     <i>
@@ -1943,7 +4267,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of How many helped" fld="6" baseField="0" baseItem="0" numFmtId="1"/>
+    <dataField name="Sum of How many people did you help during this time block?" fld="7" baseField="0" baseItem="0" numFmtId="1"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1958,14 +4282,14 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Campus" xr10:uid="{5AEAF3E2-EDDB-427F-BDDB-6080CB58758A}" sourceName="Campus">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Campus" xr10:uid="{6FFC4AAF-2EDA-4E74-8ACB-DDEBAB39CD72}" sourceName="Campus">
   <pivotTables>
-    <pivotTable tabId="8" name="ptSlicerHost"/>
-    <pivotTable tabId="5" name="ptWeekly"/>
-    <pivotTable tabId="6" name="ptMonthly"/>
+    <pivotTable tabId="9" name="ptSlicerHost"/>
+    <pivotTable tabId="6" name="ptWeekly"/>
+    <pivotTable tabId="7" name="ptMonthly"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="957050663">
+    <tabular pivotCacheId="1083663819">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -1975,14 +4299,14 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Time_block" xr10:uid="{3300AB7B-718B-4B90-B037-CAD538603E9B}" sourceName="Time block">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Time_block_this_submission_covers" xr10:uid="{77A5B991-6AC6-45AF-A5F8-03B3853F763F}" sourceName="Time block this submission covers">
   <pivotTables>
-    <pivotTable tabId="8" name="ptSlicerHost"/>
-    <pivotTable tabId="5" name="ptWeekly"/>
-    <pivotTable tabId="6" name="ptMonthly"/>
+    <pivotTable tabId="9" name="ptSlicerHost"/>
+    <pivotTable tabId="6" name="ptWeekly"/>
+    <pivotTable tabId="7" name="ptMonthly"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="957050663">
+    <tabular pivotCacheId="1083663819">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -1993,66 +4317,83 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="slCampus" xr10:uid="{3A380E5C-F819-4667-ABB9-0A574B9EBA8F}" cache="Slicer_Campus" caption="Campus" rowHeight="241300"/>
-  <slicer name="slTime" xr10:uid="{5FE0DFE4-072D-457D-B865-EEB8597989B3}" cache="Slicer_Time_block" caption="Time block" rowHeight="241300"/>
+  <slicer name="slCampus" xr10:uid="{4E123A26-8547-46FC-89A9-A1181CAB6CB7}" cache="Slicer_Campus" caption="Campus" rowHeight="241300"/>
+  <slicer name="slTime" xr10:uid="{E5DBE88E-79C5-4F2E-A7C5-78D757E966C8}" cache="Slicer_Time_block_this_submission_covers" caption="Time block" rowHeight="241300"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblVisitor" displayName="tblVisitor" ref="A1:AF4">
-  <autoFilter ref="A1:AF4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Submission ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Submitted at"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Name"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblVisitor" displayName="tblVisitor" ref="A1:AG4">
+  <autoFilter ref="A1:AG4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="33">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Campus"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Time block"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How many helped"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Wayfinding – General"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="OneCard"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="IT Support"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Bus Pass / Transportation"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Parking"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Timetable / Registration Concern"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Student Fees / Student Financial Services"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Learning Services / Math Help / Tutors"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Want to Change Program"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Connect with Faculty / Program Coordinator / Chair"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Health Insurance"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Mental Health Support / Counselling"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Medical Clinic / Medical Care"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Housing / Accommodation"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Job Search / Career Services"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Immigration / International Student Advising Referral"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="International Transition Services"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="International Admissions – Second Program"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Library – Tech Loans / TeachMeTech"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Library – Research / Writing Consultants"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Library – Academic Integrity"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="CSI – Frosh Kits"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="CSI – Peer Advocates"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="Others"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Others (Inquiry)"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Campus"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Time block this submission covers"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="How many people did you help during this time block?"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Wayfinding"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="OneCard"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="IT Support"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Bus Pass / Transportation"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Parking"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Timetable / Registration Concern"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Student Fees / Student Financial Services"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Learning Services / Math Help / Tutors"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Want to Change Program"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Connect with Faculty / Program Coordinator / Chair"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Health Insurance"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Mental Health Support / Counselling"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Medical Clinic / Medical Care"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Housing / Accommodation"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Job Search / Career Services"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Immigration / International Student Advising Referral"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="International Transition Services"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="International Admissions - Second Program"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="Library - Tech Loans / TeachMeTech"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Library - Research / Writing Consultants"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="Library - Academic Integrity"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="CSI - Frosh Kits"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="CSI - Peer Advocates"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="Others"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="Others (Inquiry)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblOutreach" displayName="tblOutreach" ref="A1:J4">
-  <autoFilter ref="A1:J4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Submission ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Submitted at"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Name"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblOutreach" displayName="tblOutreach" ref="A1:I4">
+  <autoFilter ref="A1:I4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Id"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Start time"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Completion time"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Email"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Campus"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Date of activity"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="How many helped"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Outreach Activity"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Other activity (text)"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Notes"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Name"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Campus"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Date of outreach activity"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="How many people attended the outreach activity?"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Outreach Activity"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblVisitorLong" displayName="tblVisitorLong" ref="A1:H4">
+  <autoFilter ref="A1:H4" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Id"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Completion time"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Email"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Name"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Campus"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Time block this submission covers"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Category"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Count"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2342,35 +4683,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29067E2B-495C-4DAA-8D78-B8E06795968E}">
-  <dimension ref="A1:B3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7BB1910-138A-4E77-94D7-C0C06EF0F329}">
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.46484375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="48.46484375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="24" t="s">
-        <v>112</v>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1" s="23" t="s">
+        <v>90</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="26">
+        <v>93</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="25">
+        <v>0</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="26">
+        <v>0</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="26">
+        <v>0</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="K2" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="25">
+        <v>0</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="26">
+        <v>0</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="26">
+        <v>0</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="26">
         <v>0</v>
       </c>
     </row>
@@ -2381,7 +4782,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:B35"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2396,7 +4797,7 @@
     <row r="2" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="2:2" ht="52.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:2" ht="44" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2409,12 +4810,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
@@ -2424,129 +4825,103 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="2:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="4" t="s">
+    <row r="10" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" ht="52.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="3" t="s">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="2:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:2" ht="44" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="2:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="4" t="s">
+    <row r="17" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="52.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:2" ht="100.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="3" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="2:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="2:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="4" t="s">
+    <row r="22" spans="2:2" ht="72" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:2" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" ht="20" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="2:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="4" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="2:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:2" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="58.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B30" s="3" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="2:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B34" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2556,335 +4931,317 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+    </row>
+    <row r="3" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-    </row>
-    <row r="2" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="16" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="17" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="21">
-        <f>IFERROR(SUM(tblVisitor[How many helped]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="21">
-        <f>IFERROR(SUM(tblVisitor[Wayfinding – General]),0)+IFERROR(SUM(tblVisitor[OneCard]),0)+IFERROR(SUM(tblVisitor[IT Support]),0)+IFERROR(SUM(tblVisitor[Bus Pass / Transportation]),0)+IFERROR(SUM(tblVisitor[Parking]),0)+IFERROR(SUM(tblVisitor[Timetable / Registration Concern]),0)+IFERROR(SUM(tblVisitor[Student Fees / Student Financial Services]),0)+IFERROR(SUM(tblVisitor[Learning Services / Math Help / Tutors]),0)+IFERROR(SUM(tblVisitor[Want to Change Program]),0)+IFERROR(SUM(tblVisitor[Connect with Faculty / Program Coordinator / Chair]),0)+IFERROR(SUM(tblVisitor[Health Insurance]),0)+IFERROR(SUM(tblVisitor[Mental Health Support / Counselling]),0)+IFERROR(SUM(tblVisitor[Medical Clinic / Medical Care]),0)+IFERROR(SUM(tblVisitor[Housing / Accommodation]),0)+IFERROR(SUM(tblVisitor[Job Search / Career Services]),0)+IFERROR(SUM(tblVisitor[Immigration / International Student Advising Referral]),0)+IFERROR(SUM(tblVisitor[International Transition Services]),0)+IFERROR(SUM(tblVisitor[International Admissions – Second Program]),0)+IFERROR(SUM(tblVisitor[Library – Tech Loans / TeachMeTech]),0)+IFERROR(SUM(tblVisitor[Library – Research / Writing Consultants]),0)+IFERROR(SUM(tblVisitor[Library – Academic Integrity]),0)+IFERROR(SUM(tblVisitor[CSI – Frosh Kits]),0)+IFERROR(SUM(tblVisitor[CSI – Peer Advocates]),0)+IFERROR(SUM(tblVisitor[Others]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="21" t="str">
+      <c r="A5" s="19">
+        <f>IFERROR(SUM(tblVisitor[How many people did you help during this time block?]),0)</f>
+        <v>0</v>
+      </c>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="19">
+        <f>IFERROR(SUM(tblVisitorLong[Count]),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="19" t="str">
         <f>IFERROR(INDEX(_Helpers!A4:A7,MATCH(MAX(_Helpers!B4:B7),_Helpers!B4:B7,0)),"—")</f>
         <v>Waterloo</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="21">
-        <f>IFERROR(SUM(tblOutreach[How many helped]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="19">
+        <f>IFERROR(SUM(tblOutreach[How many people attended the outreach activity?]),0)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
     </row>
     <row r="6" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="14" t="str">
-        <f>IF(ROWS(tblVisitor[Submission ID])=0,"No data yet",ROWS(tblVisitor[Submission ID])&amp;" submissions")</f>
+      <c r="A6" s="13" t="str">
+        <f>IFERROR(ROWS(tblVisitor[Id])&amp;" submissions","No data yet")</f>
         <v>3 submissions</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="14" t="str">
-        <f>IFERROR(MAX(_Helpers!B4:B7)&amp;" people helped","No data")</f>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="13" t="str">
+        <f>IFERROR(MAX(_Helpers!B4:B7)&amp;" people helped","")</f>
         <v>0 people helped</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="14" t="str">
-        <f>IFERROR(ROWS(tblOutreach[Submission ID])&amp;" outreach entries","")</f>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="13" t="str">
+        <f>IFERROR(ROWS(tblOutreach[Id])&amp;" outreach entries","")</f>
         <v>3 outreach entries</v>
       </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+      <c r="A7" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B9" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Waterloo",tblVisitor[Time block],"Morning (open – 12pm)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Waterloo",tblVisitor[Time block this submission covers],"Morning*"),0)</f>
         <v>0</v>
       </c>
       <c r="C9" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Waterloo",tblVisitor[Time block],"Afternoon (12 – 4pm)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Waterloo",tblVisitor[Time block this submission covers],"Afternoon*"),0)</f>
         <v>0</v>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Waterloo",tblVisitor[Time block],"Evening (4pm – close)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Waterloo",tblVisitor[Time block this submission covers],"Evening*"),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B10" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Doon",tblVisitor[Time block],"Morning (open – 12pm)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Doon",tblVisitor[Time block this submission covers],"Morning*"),0)</f>
         <v>0</v>
       </c>
       <c r="C10" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Doon",tblVisitor[Time block],"Afternoon (12 – 4pm)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Doon",tblVisitor[Time block this submission covers],"Afternoon*"),0)</f>
         <v>0</v>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Doon",tblVisitor[Time block],"Evening (4pm – close)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Doon",tblVisitor[Time block this submission covers],"Evening*"),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B11" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Reuter",tblVisitor[Time block],"Morning (open – 12pm)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Reuter",tblVisitor[Time block this submission covers],"Morning*"),0)</f>
         <v>0</v>
       </c>
       <c r="C11" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Reuter",tblVisitor[Time block],"Afternoon (12 – 4pm)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Reuter",tblVisitor[Time block this submission covers],"Afternoon*"),0)</f>
         <v>0</v>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Reuter",tblVisitor[Time block],"Evening (4pm – close)"),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Reuter",tblVisitor[Time block this submission covers],"Evening*"),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="7">
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Cambridge",tblVisitor[Time block this submission covers],"Morning*"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="7">
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Cambridge",tblVisitor[Time block this submission covers],"Afternoon*"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="7">
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Cambridge",tblVisitor[Time block this submission covers],"Evening*"),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="30" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="46" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+    </row>
+    <row r="62" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Cambridge",tblVisitor[Time block],"Morning (open – 12pm)"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Cambridge",tblVisitor[Time block],"Afternoon (12 – 4pm)"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Cambridge",tblVisitor[Time block],"Evening (4pm – close)"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="17" t="s">
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+    </row>
+    <row r="63" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="31" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-    </row>
-    <row r="47" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-    </row>
-    <row r="60" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A61" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="15"/>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
-      <c r="H62" s="15"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A63" s="15"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A64" s="15"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A62:H64"/>
+  <mergeCells count="21">
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A63:H65"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J4:L4"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="J5:L5"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:D12">
@@ -2913,143 +5270,149 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="29" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="36" customWidth="1"/>
-    <col min="14" max="14" width="45" customWidth="1"/>
-    <col min="15" max="15" width="42" customWidth="1"/>
-    <col min="16" max="16" width="26" customWidth="1"/>
-    <col min="17" max="17" width="50" customWidth="1"/>
-    <col min="18" max="18" width="20" customWidth="1"/>
-    <col min="19" max="19" width="39" customWidth="1"/>
-    <col min="20" max="20" width="33" customWidth="1"/>
-    <col min="21" max="21" width="27" customWidth="1"/>
-    <col min="22" max="22" width="32" customWidth="1"/>
-    <col min="23" max="23" width="50" customWidth="1"/>
-    <col min="24" max="24" width="37" customWidth="1"/>
-    <col min="25" max="25" width="45" customWidth="1"/>
-    <col min="26" max="26" width="38" customWidth="1"/>
-    <col min="27" max="27" width="44" customWidth="1"/>
-    <col min="28" max="28" width="32" customWidth="1"/>
-    <col min="29" max="29" width="20" customWidth="1"/>
-    <col min="30" max="30" width="24" customWidth="1"/>
-    <col min="31" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="20" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="37" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="9" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="29" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="36" customWidth="1"/>
+    <col min="15" max="15" width="45" customWidth="1"/>
+    <col min="16" max="16" width="42" customWidth="1"/>
+    <col min="17" max="17" width="26" customWidth="1"/>
+    <col min="18" max="18" width="50" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="39" customWidth="1"/>
+    <col min="21" max="21" width="33" customWidth="1"/>
+    <col min="22" max="22" width="27" customWidth="1"/>
+    <col min="23" max="23" width="32" customWidth="1"/>
+    <col min="24" max="24" width="50" customWidth="1"/>
+    <col min="25" max="25" width="37" customWidth="1"/>
+    <col min="26" max="26" width="45" customWidth="1"/>
+    <col min="27" max="27" width="38" customWidth="1"/>
+    <col min="28" max="28" width="44" customWidth="1"/>
+    <col min="29" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="20" customWidth="1"/>
+    <col min="31" max="31" width="24" customWidth="1"/>
+    <col min="32" max="32" width="14" customWidth="1"/>
+    <col min="33" max="33" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:33" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="M1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="N1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="O1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="R1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="S1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="T1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="U1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="V1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="W1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="X1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="Y1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="Z1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="AA1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="AB1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="AC1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="AD1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="AE1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="AF1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="AA1" s="9" t="s">
+      <c r="AG1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="AB1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE1" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF1" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B2" s="10">
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9">
         <v>45292</v>
       </c>
-      <c r="G2">
-        <v>0</v>
+      <c r="C2" s="9">
+        <v>45292</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -3123,13 +5486,19 @@
       <c r="AE2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B3" s="10">
+      <c r="AF2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9">
         <v>45458</v>
       </c>
-      <c r="G3">
-        <v>0</v>
+      <c r="C3" s="9">
+        <v>45458</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -3203,13 +5572,19 @@
       <c r="AE3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
-      <c r="B4" s="10">
+      <c r="AF3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9">
         <v>45657</v>
       </c>
-      <c r="G4">
-        <v>0</v>
+      <c r="C4" s="9">
+        <v>45657</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3281,6 +5656,9 @@
         <v>0</v>
       </c>
       <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>0</v>
       </c>
     </row>
@@ -3294,81 +5672,94 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="1" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="10">
+    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9">
         <v>45292</v>
       </c>
-      <c r="F2" s="11">
+      <c r="C2" s="9">
         <v>45292</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="10">
+      <c r="G2" s="10">
+        <v>45292</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9">
         <v>45458</v>
       </c>
-      <c r="F3" s="11">
+      <c r="C3" s="9">
         <v>45458</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="10">
+      <c r="G3" s="10">
+        <v>45458</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9">
         <v>45657</v>
       </c>
-      <c r="F4" s="11">
+      <c r="C4" s="9">
         <v>45657</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="10">
+        <v>45657</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
     </row>
@@ -3382,144 +5773,89 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B1:H15"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="37" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B1" s="12" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="90" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B10" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B11" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="10">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9">
         <v>45292</v>
       </c>
-      <c r="C12" s="27">
-        <v>0</v>
-      </c>
-      <c r="D12" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="10">
+      <c r="G2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9">
         <v>45458</v>
       </c>
-      <c r="C13" s="27">
-        <v>0</v>
-      </c>
-      <c r="D13" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="10">
+      <c r="G3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9">
         <v>45657</v>
       </c>
-      <c r="C14" s="27">
-        <v>0</v>
-      </c>
-      <c r="D14" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="27">
-        <v>0</v>
-      </c>
-      <c r="D15" s="27">
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:H8"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -3529,138 +5865,129 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="B1" s="12" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="90" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+      <c r="B1" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="70.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B10" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>37</v>
+      <c r="B10" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B11" s="24" t="s">
-        <v>53</v>
+      <c r="B11" s="23" t="s">
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>45292</v>
       </c>
-      <c r="C12" s="27">
-        <v>0</v>
-      </c>
-      <c r="D12" s="27">
+      <c r="C12" s="26">
+        <v>0</v>
+      </c>
+      <c r="D12" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>45458</v>
       </c>
-      <c r="C13" s="27">
-        <v>0</v>
-      </c>
-      <c r="D13" s="27">
+      <c r="C13" s="26">
+        <v>0</v>
+      </c>
+      <c r="D13" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>45657</v>
       </c>
-      <c r="C14" s="27">
-        <v>0</v>
-      </c>
-      <c r="D14" s="27">
+      <c r="C14" s="26">
+        <v>0</v>
+      </c>
+      <c r="D14" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="27">
-        <v>0</v>
-      </c>
-      <c r="D15" s="27">
+      <c r="B15" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="26">
+        <v>0</v>
+      </c>
+      <c r="D15" s="26">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B3:H8"/>
+    <mergeCell ref="B3:H7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3668,440 +5995,198 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="B1:H15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="10" max="10" width="36" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="13" max="13" width="36" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="52.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="B1" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="70.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B10" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B11" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="D1" s="23" t="s">
+      <c r="D11" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="G1" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="H1" s="15"/>
-      <c r="J1" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="K1" s="15"/>
-      <c r="M1" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="15"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" s="13" t="s">
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B12" s="9">
+        <v>45292</v>
+      </c>
+      <c r="C12" s="26">
+        <v>0</v>
+      </c>
+      <c r="D12" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B13" s="9">
+        <v>45458</v>
+      </c>
+      <c r="C13" s="26">
+        <v>0</v>
+      </c>
+      <c r="D13" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B14" s="9">
+        <v>45657</v>
+      </c>
+      <c r="C14" s="26">
+        <v>0</v>
+      </c>
+      <c r="D14" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B15" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="26">
+        <v>0</v>
+      </c>
+      <c r="D15" s="26">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:H7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="14"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" s="13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>41</v>
-      </c>
       <c r="B4">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Waterloo"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="G4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4">
-        <f>IFERROR(SUM(tblVisitor[Wayfinding – General]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"Bell Let's Talk"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Campus],"Waterloo"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Waterloo"),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B5">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Doon"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="G5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5">
-        <f>IFERROR(SUM(tblVisitor[OneCard]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>103</v>
-      </c>
-      <c r="K5">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"Black History Month"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Campus],"Doon"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Doon"),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B6">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Reuter"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="G6" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6">
-        <f>IFERROR(SUM(tblVisitor[IT Support]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>104</v>
-      </c>
-      <c r="K6">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"Campus Welcome Day"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Campus],"Reuter"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Reuter"),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many helped],tblVisitor[Campus],"Cambridge"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="G7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7">
-        <f>IFERROR(SUM(tblVisitor[Bus Pass / Transportation]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K7">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"CCR and SSP Promotion"),0)</f>
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N7">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Campus],"Cambridge"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="G8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8">
-        <f>IFERROR(SUM(tblVisitor[Parking]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>106</v>
-      </c>
-      <c r="K8">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"Celebrating Diversity"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="G9" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9">
-        <f>IFERROR(SUM(tblVisitor[Timetable / Registration Concern]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>107</v>
-      </c>
-      <c r="K9">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"Health and Wellness Outreach"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="G10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10">
-        <f>IFERROR(SUM(tblVisitor[Student Fees / Student Financial Services]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>108</v>
-      </c>
-      <c r="K10">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"International Women's Day"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="G11" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11">
-        <f>IFERROR(SUM(tblVisitor[Learning Services / Math Help / Tutors]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>109</v>
-      </c>
-      <c r="K11">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"Pride Month"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="G12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12">
-        <f>IFERROR(SUM(tblVisitor[Want to Change Program]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>110</v>
-      </c>
-      <c r="K12">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"Sexual Health Week"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="G13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13">
-        <f>IFERROR(SUM(tblVisitor[Connect with Faculty / Program Coordinator / Chair]),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>111</v>
-      </c>
-      <c r="K13">
-        <f>IFERROR(SUMIFS(tblOutreach[How many helped],tblOutreach[Outreach Activity],"Other"),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="G14" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14">
-        <f>IFERROR(SUM(tblVisitor[Health Insurance]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="G15" t="s">
-        <v>69</v>
-      </c>
-      <c r="H15">
-        <f>IFERROR(SUM(tblVisitor[Mental Health Support / Counselling]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="G16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16">
-        <f>IFERROR(SUM(tblVisitor[Medical Clinic / Medical Care]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G17" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17">
-        <f>IFERROR(SUM(tblVisitor[Housing / Accommodation]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H18">
-        <f>IFERROR(SUM(tblVisitor[Job Search / Career Services]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G19" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19">
-        <f>IFERROR(SUM(tblVisitor[Immigration / International Student Advising Referral]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G20" t="s">
-        <v>74</v>
-      </c>
-      <c r="H20">
-        <f>IFERROR(SUM(tblVisitor[International Transition Services]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G21" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21">
-        <f>IFERROR(SUM(tblVisitor[International Admissions – Second Program]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G22" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22">
-        <f>IFERROR(SUM(tblVisitor[Library – Tech Loans / TeachMeTech]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G23" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23">
-        <f>IFERROR(SUM(tblVisitor[Library – Research / Writing Consultants]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G24" t="s">
-        <v>78</v>
-      </c>
-      <c r="H24">
-        <f>IFERROR(SUM(tblVisitor[Library – Academic Integrity]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G25" t="s">
-        <v>79</v>
-      </c>
-      <c r="H25">
-        <f>IFERROR(SUM(tblVisitor[CSI – Frosh Kits]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G26" t="s">
-        <v>80</v>
-      </c>
-      <c r="H26">
-        <f>IFERROR(SUM(tblVisitor[CSI – Peer Advocates]),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="7:8" x14ac:dyDescent="0.45">
-      <c r="G27" t="s">
-        <v>81</v>
-      </c>
-      <c r="H27">
-        <f>IFERROR(SUM(tblVisitor[Others]),0)</f>
+        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Cambridge"),0)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="D4:E10"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/student-engagement-dashboard-starter.xlsx
+++ b/templates/student-engagement-dashboard-starter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\Project Files\Github\student-engagement\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFAD3B4-AFF1-4C0C-8960-8F200BE9DCA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3D97D7-6319-4134-962F-708C1E810F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="95">
   <si>
     <t>How to use this workbook (v2 — long-format)</t>
   </si>
@@ -167,9 +167,6 @@
   </si>
   <si>
     <t>Afternoon</t>
-  </si>
-  <si>
-    <t>Evening</t>
   </si>
   <si>
     <t>Waterloo</t>
@@ -705,7 +702,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-B30B-4A8A-9296-1D384DB80283}"/>
+              <c16:uniqueId val="{0000000B-94C8-4EDF-82BB-21F83DEFD3E1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -719,11 +716,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="972983744"/>
-        <c:axId val="972991904"/>
+        <c:axId val="114690992"/>
+        <c:axId val="114718352"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="972983744"/>
+        <c:axId val="114690992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -766,7 +763,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="972991904"/>
+        <c:crossAx val="114718352"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -774,7 +771,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="972991904"/>
+        <c:axId val="114718352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -825,7 +822,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="972983744"/>
+        <c:crossAx val="114690992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1028,7 +1025,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-0D59-4E75-BC65-27D4494E809F}"/>
+              <c16:uniqueId val="{0000000B-1B24-4062-8DF0-D2F210CDCEEA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1042,11 +1039,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="972990944"/>
-        <c:axId val="972982784"/>
+        <c:axId val="114718832"/>
+        <c:axId val="114719312"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="972990944"/>
+        <c:axId val="114718832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1089,7 +1086,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="972982784"/>
+        <c:crossAx val="114719312"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1097,7 +1094,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="972982784"/>
+        <c:axId val="114719312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1148,7 +1145,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="972990944"/>
+        <c:crossAx val="114718832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1351,7 +1348,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-8803-411D-B9B3-319CFC2A5D2C}"/>
+              <c16:uniqueId val="{0000000B-0F4A-4D42-941C-B0CCDE7BEA17}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1365,11 +1362,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="972978944"/>
-        <c:axId val="972992864"/>
+        <c:axId val="114725072"/>
+        <c:axId val="114725552"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="972978944"/>
+        <c:axId val="114725072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1412,7 +1409,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="972992864"/>
+        <c:crossAx val="114725552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1420,7 +1417,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="972992864"/>
+        <c:axId val="114725552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1471,7 +1468,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="972978944"/>
+        <c:crossAx val="114725072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3193,7 +3190,7 @@
             <xdr:cNvPr id="2" name="slCampus">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D600BEC0-61F6-F70E-A26D-B85C9235F9EB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CE9154D-7464-0BC2-15BC-2B5B2BD499AA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3271,7 +3268,7 @@
             <xdr:cNvPr id="3" name="slTime">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C95D746-F290-0B59-E45C-8E8942C676A9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D41E4B91-F184-1A37-4DAF-031B172140A8}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3347,7 +3344,7 @@
         <xdr:cNvPr id="4" name="chTopCategories">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B5FF3B-C1E9-9946-ACC0-C0E1A1EDF5E9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAD7C1B7-1E82-DBAB-790A-554894475908}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3383,7 +3380,7 @@
         <xdr:cNvPr id="5" name="chOutreachThemes">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D69364F0-CCEB-3CB5-5E59-87627B001B7D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{084F433F-6154-2083-3FD3-5CAE8CAE2067}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3419,7 +3416,7 @@
         <xdr:cNvPr id="6" name="chOutreachByCampus">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6800CA24-29A9-963E-E506-F7D706396A3D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5524B474-1756-F5DE-0EE4-EC9C644B543B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3441,7 +3438,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.820775231485" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{487A8BB3-6719-4684-A36E-D58B084C6269}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.909967245374" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{15E29573-6556-460B-B42C-E8895C5CF0D0}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblVisitor"/>
   </cacheSource>
@@ -3556,14 +3553,14 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="1083663819"/>
+      <x14:pivotCacheDefinition pivotCacheId="1720447323"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.820779166665" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{29FDED5C-D45E-410C-A1AF-024DD98828B8}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.909968981483" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{FB1B596D-3A38-43C1-B11C-C29472C024FC}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblVisitorLong"/>
   </cacheSource>
@@ -3604,7 +3601,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.820788888886" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{BCDBE610-5152-4118-B353-CCCC8F7BCE83}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.909971064815" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{2E899657-6675-4E31-801E-2DDC6905AD6D}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblOutreach"/>
   </cacheSource>
@@ -3833,7 +3830,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{16C8CC98-62E0-4963-817E-18A684A81D2E}" name="ptOutreachByCampus" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{445CCE66-0C77-4ADA-8D39-E361D39B3973}" name="ptOutreachByCampus" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="J1:K3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -3892,7 +3889,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7E51020-C0DC-4E0E-BC9C-98DFD9107402}" name="ptOutreachThemes" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A5839FE-CDC3-41F0-872B-CBF1238A199C}" name="ptOutreachThemes" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="G1:H3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -3951,7 +3948,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EAA0FC79-74EC-462F-8883-BC857E166A82}" name="ptTopCategories" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B2429748-13AC-47EB-A479-75BF456C5E71}" name="ptTopCategories" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -4009,7 +4006,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BC194E73-8C73-4EA3-BE42-A5387AD0CDAA}" name="ptSlicerHost" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D2632FF1-CC1C-4EEA-B938-480EA2E86A63}" name="ptSlicerHost" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField showAll="0"/>
@@ -4086,7 +4083,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B3D2BBFF-1ED6-44F6-AF36-6A915727236E}" name="ptWeekly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC2CE0DE-279C-49DE-AE78-0B25BA0D594A}" name="ptWeekly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B10:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -4184,7 +4181,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E1519812-928F-49FB-9BB8-9A18DC4B6F78}" name="ptMonthly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3EB5CEA2-D40C-44E3-BE49-AB2DE4A7C27E}" name="ptMonthly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B10:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -4282,14 +4279,14 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Campus" xr10:uid="{6FFC4AAF-2EDA-4E74-8ACB-DDEBAB39CD72}" sourceName="Campus">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Campus" xr10:uid="{90926E5A-871A-47DF-8A96-4B397F03F501}" sourceName="Campus">
   <pivotTables>
     <pivotTable tabId="9" name="ptSlicerHost"/>
     <pivotTable tabId="6" name="ptWeekly"/>
     <pivotTable tabId="7" name="ptMonthly"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1083663819">
+    <tabular pivotCacheId="1720447323">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -4299,14 +4296,14 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Time_block_this_submission_covers" xr10:uid="{77A5B991-6AC6-45AF-A5F8-03B3853F763F}" sourceName="Time block this submission covers">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Time_block_this_submission_covers" xr10:uid="{BD82BD19-4ED7-486E-B6B2-D1C2096EE3F9}" sourceName="Time block this submission covers">
   <pivotTables>
     <pivotTable tabId="9" name="ptSlicerHost"/>
     <pivotTable tabId="6" name="ptWeekly"/>
     <pivotTable tabId="7" name="ptMonthly"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1083663819">
+    <tabular pivotCacheId="1720447323">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -4317,8 +4314,8 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="slCampus" xr10:uid="{4E123A26-8547-46FC-89A9-A1181CAB6CB7}" cache="Slicer_Campus" caption="Campus" rowHeight="241300"/>
-  <slicer name="slTime" xr10:uid="{E5DBE88E-79C5-4F2E-A7C5-78D757E966C8}" cache="Slicer_Time_block_this_submission_covers" caption="Time block" rowHeight="241300"/>
+  <slicer name="slCampus" xr10:uid="{0AFB37A0-7B1A-4099-9AD9-DAC3CFA79AF5}" cache="Slicer_Campus" caption="Campus" rowHeight="241300"/>
+  <slicer name="slTime" xr10:uid="{2CD86B23-26C0-44CA-B022-39E09C9D813E}" cache="Slicer_Time_block_this_submission_covers" caption="Time block" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -4683,7 +4680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7BB1910-138A-4E77-94D7-C0C06EF0F329}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{536AEC31-D21E-4C2F-9BD3-AB97CD3DA31E}">
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -4699,51 +4696,51 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="G1" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" t="s">
-        <v>95</v>
-      </c>
       <c r="J1" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B2" s="25">
         <v>0</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2" s="26">
         <v>0</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H2" s="26">
         <v>0</v>
       </c>
       <c r="J2" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K2" s="26">
         <v>0</v>
@@ -4751,25 +4748,25 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="25">
         <v>0</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E3" s="26">
         <v>0</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H3" s="26">
         <v>0</v>
       </c>
       <c r="J3" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K3" s="26">
         <v>0</v>
@@ -5068,13 +5065,10 @@
       <c r="C8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="9" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="7">
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Waterloo",tblVisitor[Time block this submission covers],"Morning*"),0)</f>
@@ -5084,14 +5078,10 @@
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Waterloo",tblVisitor[Time block this submission covers],"Afternoon*"),0)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Waterloo",tblVisitor[Time block this submission covers],"Evening*"),0)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="10" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="7">
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Doon",tblVisitor[Time block this submission covers],"Morning*"),0)</f>
@@ -5101,14 +5091,10 @@
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Doon",tblVisitor[Time block this submission covers],"Afternoon*"),0)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Doon",tblVisitor[Time block this submission covers],"Evening*"),0)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="7">
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Reuter",tblVisitor[Time block this submission covers],"Morning*"),0)</f>
@@ -5118,14 +5104,10 @@
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Reuter",tblVisitor[Time block this submission covers],"Afternoon*"),0)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Reuter",tblVisitor[Time block this submission covers],"Evening*"),0)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:12" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="7">
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Cambridge",tblVisitor[Time block this submission covers],"Morning*"),0)</f>
@@ -5135,14 +5117,10 @@
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Cambridge",tblVisitor[Time block this submission covers],"Afternoon*"),0)</f>
         <v>0</v>
       </c>
-      <c r="D12" s="7">
-        <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Cambridge",tblVisitor[Time block this submission covers],"Evening*"),0)</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="14" spans="1:12" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -5154,7 +5132,7 @@
     </row>
     <row r="30" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -5166,7 +5144,7 @@
     </row>
     <row r="46" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -5178,7 +5156,7 @@
     </row>
     <row r="62" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -5190,7 +5168,7 @@
     </row>
     <row r="63" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -5244,7 +5222,7 @@
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="J5:L5"/>
   </mergeCells>
-  <conditionalFormatting sqref="B9:D12">
+  <conditionalFormatting sqref="B9:C12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5305,103 +5283,103 @@
   <sheetData>
     <row r="1" spans="1:33" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>33</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AD1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AE1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AF1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="AF1" s="8" t="s">
+      <c r="AG1" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="AG1" s="8" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.45">
@@ -5685,31 +5663,31 @@
   <sheetData>
     <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>33</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
@@ -5785,28 +5763,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -5817,7 +5795,7 @@
         <v>45292</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -5831,7 +5809,7 @@
         <v>45458</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -5845,7 +5823,7 @@
         <v>45657</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5872,12 +5850,12 @@
   <sheetData>
     <row r="1" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B1" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="70.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
@@ -5924,7 +5902,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B10" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>33</v>
@@ -5932,13 +5910,13 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B11" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
         <v>91</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
@@ -5976,7 +5954,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B15" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="26">
         <v>0</v>
@@ -6006,12 +5984,12 @@
   <sheetData>
     <row r="1" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B1" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="70.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
@@ -6058,7 +6036,7 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B10" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>33</v>
@@ -6066,13 +6044,13 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B11" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
         <v>91</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
@@ -6110,7 +6088,7 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B15" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="26">
         <v>0</v>
@@ -6137,7 +6115,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="14"/>
     </row>
@@ -6146,12 +6124,12 @@
         <v>33</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Waterloo"),0)</f>
@@ -6160,7 +6138,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Doon"),0)</f>
@@ -6169,7 +6147,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Reuter"),0)</f>
@@ -6178,7 +6156,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <f>IFERROR(SUMIFS(tblVisitor[How many people did you help during this time block?],tblVisitor[Campus],"Cambridge"),0)</f>

--- a/templates/student-engagement-dashboard-starter.xlsx
+++ b/templates/student-engagement-dashboard-starter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\Project Files\Github\student-engagement\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3D97D7-6319-4134-962F-708C1E810F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B78381F-E7FD-49E6-91BB-E7DEABBCEBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -702,7 +702,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-94C8-4EDF-82BB-21F83DEFD3E1}"/>
+              <c16:uniqueId val="{0000000B-D9BB-46F9-A1CE-325219A356CD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -716,11 +716,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="114690992"/>
-        <c:axId val="114718352"/>
+        <c:axId val="1655276575"/>
+        <c:axId val="1655273215"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="114690992"/>
+        <c:axId val="1655276575"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -763,7 +763,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="114718352"/>
+        <c:crossAx val="1655273215"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -771,7 +771,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="114718352"/>
+        <c:axId val="1655273215"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -822,7 +822,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="114690992"/>
+        <c:crossAx val="1655276575"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1025,7 +1025,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-1B24-4062-8DF0-D2F210CDCEEA}"/>
+              <c16:uniqueId val="{0000000B-AA1A-46BB-A9D0-0703B046F4B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1039,11 +1039,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="114718832"/>
-        <c:axId val="114719312"/>
+        <c:axId val="1657044783"/>
+        <c:axId val="1657046223"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="114718832"/>
+        <c:axId val="1657044783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1086,7 +1086,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="114719312"/>
+        <c:crossAx val="1657046223"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1094,7 +1094,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="114719312"/>
+        <c:axId val="1657046223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1145,7 +1145,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="114718832"/>
+        <c:crossAx val="1657044783"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1348,7 +1348,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-0F4A-4D42-941C-B0CCDE7BEA17}"/>
+              <c16:uniqueId val="{0000000B-CEF2-498A-A8D2-419DDDEC1456}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1362,11 +1362,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="114725072"/>
-        <c:axId val="114725552"/>
+        <c:axId val="1689541023"/>
+        <c:axId val="1689540063"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="114725072"/>
+        <c:axId val="1689541023"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1409,7 +1409,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="114725552"/>
+        <c:crossAx val="1689540063"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1417,7 +1417,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="114725552"/>
+        <c:axId val="1689540063"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1468,7 +1468,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="114725072"/>
+        <c:crossAx val="1689541023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3190,7 +3190,7 @@
             <xdr:cNvPr id="2" name="slCampus">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CE9154D-7464-0BC2-15BC-2B5B2BD499AA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2519DC2A-3064-C4E3-FB34-BC3A949330DD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3268,7 +3268,7 @@
             <xdr:cNvPr id="3" name="slTime">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D41E4B91-F184-1A37-4DAF-031B172140A8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75463019-B81C-22CC-B923-626402C34FD3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3344,7 +3344,7 @@
         <xdr:cNvPr id="4" name="chTopCategories">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAD7C1B7-1E82-DBAB-790A-554894475908}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF4F240B-5FC9-DC17-D8FC-679D8E5B6ECB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3380,7 +3380,7 @@
         <xdr:cNvPr id="5" name="chOutreachThemes">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{084F433F-6154-2083-3FD3-5CAE8CAE2067}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A1EA85E-1EE1-5068-2DB8-962EA082871C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3416,7 +3416,7 @@
         <xdr:cNvPr id="6" name="chOutreachByCampus">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5524B474-1756-F5DE-0EE4-EC9C644B543B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3932D8E-4814-B889-C74D-069CCFAC7970}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3438,7 +3438,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.909967245374" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{15E29573-6556-460B-B42C-E8895C5CF0D0}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.918485416667" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{3F104E7A-8C07-4276-98A4-879A5F04A823}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblVisitor"/>
   </cacheSource>
@@ -3553,14 +3553,14 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="1720447323"/>
+      <x14:pivotCacheDefinition pivotCacheId="716333530"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.909968981483" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{FB1B596D-3A38-43C1-B11C-C29472C024FC}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.918488078707" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{9B9C7C03-C9F8-4C16-82C1-ED5751AE2227}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblVisitorLong"/>
   </cacheSource>
@@ -3601,7 +3601,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.909971064815" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{2E899657-6675-4E31-801E-2DDC6905AD6D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.918489814816" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{6D18B7C2-3AD9-4C5B-A2EC-40EA72E4E21E}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblOutreach"/>
   </cacheSource>
@@ -3830,7 +3830,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{445CCE66-0C77-4ADA-8D39-E361D39B3973}" name="ptOutreachByCampus" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F60A1B92-2C6C-4A72-9732-139FFA979D59}" name="ptOutreachByCampus" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="J1:K3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -3889,7 +3889,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8A5839FE-CDC3-41F0-872B-CBF1238A199C}" name="ptOutreachThemes" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E244B785-C4B8-4F4C-BFBB-91911063FA07}" name="ptOutreachThemes" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="G1:H3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -3948,7 +3948,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B2429748-13AC-47EB-A479-75BF456C5E71}" name="ptTopCategories" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F81A376A-57B2-4D3A-976B-E2A1FB335487}" name="ptTopCategories" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -4006,7 +4006,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D2632FF1-CC1C-4EEA-B938-480EA2E86A63}" name="ptSlicerHost" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8E3A76D-E36B-4C66-B6AF-FED0A7021955}" name="ptSlicerHost" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField showAll="0"/>
@@ -4083,7 +4083,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EC2CE0DE-279C-49DE-AE78-0B25BA0D594A}" name="ptWeekly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65A70C08-C4A3-4602-8846-13524AB14E2B}" name="ptWeekly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B10:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -4181,7 +4181,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3EB5CEA2-D40C-44E3-BE49-AB2DE4A7C27E}" name="ptMonthly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38ECA955-0239-4850-9452-0D49E5EA8943}" name="ptMonthly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B10:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -4279,14 +4279,14 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Campus" xr10:uid="{90926E5A-871A-47DF-8A96-4B397F03F501}" sourceName="Campus">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Campus" xr10:uid="{A8A8AF23-6B14-4997-9A14-16D1174948B2}" sourceName="Campus">
   <pivotTables>
     <pivotTable tabId="9" name="ptSlicerHost"/>
     <pivotTable tabId="6" name="ptWeekly"/>
     <pivotTable tabId="7" name="ptMonthly"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1720447323">
+    <tabular pivotCacheId="716333530">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -4296,14 +4296,14 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Time_block_this_submission_covers" xr10:uid="{BD82BD19-4ED7-486E-B6B2-D1C2096EE3F9}" sourceName="Time block this submission covers">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Time_block_this_submission_covers" xr10:uid="{76158DB2-C97D-4CAB-82B1-30598A8C811E}" sourceName="Time block this submission covers">
   <pivotTables>
     <pivotTable tabId="9" name="ptSlicerHost"/>
     <pivotTable tabId="6" name="ptWeekly"/>
     <pivotTable tabId="7" name="ptMonthly"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="1720447323">
+    <tabular pivotCacheId="716333530">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -4314,8 +4314,8 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="slCampus" xr10:uid="{0AFB37A0-7B1A-4099-9AD9-DAC3CFA79AF5}" cache="Slicer_Campus" caption="Campus" rowHeight="241300"/>
-  <slicer name="slTime" xr10:uid="{2CD86B23-26C0-44CA-B022-39E09C9D813E}" cache="Slicer_Time_block_this_submission_covers" caption="Time block" rowHeight="241300"/>
+  <slicer name="slCampus" xr10:uid="{49CDC992-1D9D-4589-B40A-C409BB7374BD}" cache="Slicer_Campus" caption="Campus" rowHeight="241300"/>
+  <slicer name="slTime" xr10:uid="{F4CD45CC-DCC4-4633-9C2E-C14D8F3CD2C4}" cache="Slicer_Time_block_this_submission_covers" caption="Time block" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -4680,7 +4680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{536AEC31-D21E-4C2F-9BD3-AB97CD3DA31E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BCE8E1-B6A4-44F5-AFF9-2CFE7C6765B2}">
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -5020,7 +5020,7 @@
     </row>
     <row r="6" spans="1:12" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="str">
-        <f>IFERROR(ROWS(tblVisitor[Id])&amp;" submissions","No data yet")</f>
+        <f>IFERROR(_xlfn.SINGLE(ROWS(tblVisitor[Id]))&amp;" submissions","No data yet")</f>
         <v>3 submissions</v>
       </c>
       <c r="B6" s="14"/>
@@ -5037,7 +5037,7 @@
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="13" t="str">
-        <f>IFERROR(ROWS(tblOutreach[Id])&amp;" outreach entries","")</f>
+        <f>IFERROR(_xlfn.SINGLE(ROWS(tblOutreach[Id]))&amp;" outreach entries","")</f>
         <v>3 outreach entries</v>
       </c>
       <c r="K6" s="14"/>

--- a/templates/student-engagement-dashboard-starter.xlsx
+++ b/templates/student-engagement-dashboard-starter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Documents\Project Files\Github\student-engagement\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B78381F-E7FD-49E6-91BB-E7DEABBCEBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D94FEF6-9DFB-4624-854D-EC980550073C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,9 +29,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="7" r:id="rId10"/>
-    <pivotCache cacheId="11" r:id="rId11"/>
-    <pivotCache cacheId="17" r:id="rId12"/>
+    <pivotCache cacheId="8" r:id="rId10"/>
+    <pivotCache cacheId="13" r:id="rId11"/>
+    <pivotCache cacheId="20" r:id="rId12"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -702,7 +702,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-D9BB-46F9-A1CE-325219A356CD}"/>
+              <c16:uniqueId val="{0000000B-AC7C-4C01-9541-BD9FA3EBBF34}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -716,11 +716,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1655276575"/>
-        <c:axId val="1655273215"/>
+        <c:axId val="1814496399"/>
+        <c:axId val="1814498319"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1655276575"/>
+        <c:axId val="1814496399"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -763,7 +763,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1655273215"/>
+        <c:crossAx val="1814498319"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -771,7 +771,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1655273215"/>
+        <c:axId val="1814498319"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -822,7 +822,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1655276575"/>
+        <c:crossAx val="1814496399"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1025,7 +1025,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-AA1A-46BB-A9D0-0703B046F4B7}"/>
+              <c16:uniqueId val="{0000000B-E097-456A-A9DD-542AB29E5B2A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1039,11 +1039,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1657044783"/>
-        <c:axId val="1657046223"/>
+        <c:axId val="1816751119"/>
+        <c:axId val="1816748719"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1657044783"/>
+        <c:axId val="1816751119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1086,7 +1086,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1657046223"/>
+        <c:crossAx val="1816748719"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1094,7 +1094,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1657046223"/>
+        <c:axId val="1816748719"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1145,7 +1145,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1657044783"/>
+        <c:crossAx val="1816751119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1348,7 +1348,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-CEF2-498A-A8D2-419DDDEC1456}"/>
+              <c16:uniqueId val="{0000000B-E8EB-4D7F-8CF7-2C2199EC62F9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1362,11 +1362,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1689541023"/>
-        <c:axId val="1689540063"/>
+        <c:axId val="1854031007"/>
+        <c:axId val="1816749679"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1689541023"/>
+        <c:axId val="1854031007"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1409,7 +1409,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1689540063"/>
+        <c:crossAx val="1816749679"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1417,7 +1417,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1689540063"/>
+        <c:axId val="1816749679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1468,7 +1468,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1689541023"/>
+        <c:crossAx val="1854031007"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3190,7 +3190,7 @@
             <xdr:cNvPr id="2" name="slCampus">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2519DC2A-3064-C4E3-FB34-BC3A949330DD}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2EE4573-54C7-6B75-D50D-4DB992D5CFB2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3268,7 +3268,7 @@
             <xdr:cNvPr id="3" name="slTime">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75463019-B81C-22CC-B923-626402C34FD3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F35D2769-93D8-575F-2BC0-632D18940492}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3344,7 +3344,7 @@
         <xdr:cNvPr id="4" name="chTopCategories">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF4F240B-5FC9-DC17-D8FC-679D8E5B6ECB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F93B42A-FC36-95F0-48AB-7AD7DDE2CBD0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3380,7 +3380,7 @@
         <xdr:cNvPr id="5" name="chOutreachThemes">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A1EA85E-1EE1-5068-2DB8-962EA082871C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80E1728B-40C2-780E-355E-A7A4647FE2C8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3416,7 +3416,7 @@
         <xdr:cNvPr id="6" name="chOutreachByCampus">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3932D8E-4814-B889-C74D-069CCFAC7970}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02397C22-D70E-92FE-9E0E-DC962C88580C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3438,7 +3438,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.918485416667" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{3F104E7A-8C07-4276-98A4-879A5F04A823}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.93053287037" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{2ABCB577-52BC-4E4D-91C5-C28F5FC06EA9}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblVisitor"/>
   </cacheSource>
@@ -3553,14 +3553,14 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition pivotCacheId="716333530"/>
+      <x14:pivotCacheDefinition pivotCacheId="152915111"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.918488078707" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{9B9C7C03-C9F8-4C16-82C1-ED5751AE2227}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.930535763888" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{202BFA7F-673C-4F93-9587-1BE8E001AEC9}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblVisitorLong"/>
   </cacheSource>
@@ -3601,7 +3601,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.918489814816" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{6D18B7C2-3AD9-4C5B-A2EC-40EA72E4E21E}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Gabriel Elias Gabrie Kattan" refreshedDate="46147.930537499997" missingItemsLimit="0" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{31244992-C4C3-4025-A1AA-15315E0517FE}">
   <cacheSource type="worksheet">
     <worksheetSource name="tblOutreach"/>
   </cacheSource>
@@ -3830,7 +3830,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F60A1B92-2C6C-4A72-9732-139FFA979D59}" name="ptOutreachByCampus" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0654080-B3C3-474D-B59C-F6ACDBD90DE0}" name="ptOutreachByCampus" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="J1:K3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -3889,7 +3889,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E244B785-C4B8-4F4C-BFBB-91911063FA07}" name="ptOutreachThemes" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CEC00D65-9352-4E08-B9EB-5200F62C285A}" name="ptOutreachThemes" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="G1:H3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -3948,7 +3948,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F81A376A-57B2-4D3A-976B-E2A1FB335487}" name="ptTopCategories" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{339DA5B3-981A-41A5-AEAE-1A188337D4F2}" name="ptTopCategories" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="D1:E3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -4006,7 +4006,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8E3A76D-E36B-4C66-B6AF-FED0A7021955}" name="ptSlicerHost" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FCFFBFB-17FB-4088-B5E0-33A6001E8387}" name="ptSlicerHost" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:B3" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField showAll="0"/>
@@ -4083,7 +4083,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{65A70C08-C4A3-4602-8846-13524AB14E2B}" name="ptWeekly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5030020B-089C-4E84-ACA6-F138E1025A3A}" name="ptWeekly" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B10:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -4181,7 +4181,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38ECA955-0239-4850-9452-0D49E5EA8943}" name="ptMonthly" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C57B576A-A4E2-45C5-9C7F-2246C8DBC8CE}" name="ptMonthly" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B10:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -4279,14 +4279,14 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Campus" xr10:uid="{A8A8AF23-6B14-4997-9A14-16D1174948B2}" sourceName="Campus">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Campus" xr10:uid="{A629B34F-7BFE-43E1-854A-D7077A45BA96}" sourceName="Campus">
   <pivotTables>
     <pivotTable tabId="9" name="ptSlicerHost"/>
     <pivotTable tabId="6" name="ptWeekly"/>
     <pivotTable tabId="7" name="ptMonthly"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="716333530">
+    <tabular pivotCacheId="152915111">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -4296,14 +4296,14 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Time_block_this_submission_covers" xr10:uid="{76158DB2-C97D-4CAB-82B1-30598A8C811E}" sourceName="Time block this submission covers">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Time_block_this_submission_covers" xr10:uid="{780EE2D7-5488-4ACD-8153-D6C2D761AD6A}" sourceName="Time block this submission covers">
   <pivotTables>
     <pivotTable tabId="9" name="ptSlicerHost"/>
     <pivotTable tabId="6" name="ptWeekly"/>
     <pivotTable tabId="7" name="ptMonthly"/>
   </pivotTables>
   <data>
-    <tabular pivotCacheId="716333530">
+    <tabular pivotCacheId="152915111">
       <items count="1">
         <i x="0" s="1"/>
       </items>
@@ -4314,8 +4314,8 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="slCampus" xr10:uid="{49CDC992-1D9D-4589-B40A-C409BB7374BD}" cache="Slicer_Campus" caption="Campus" rowHeight="241300"/>
-  <slicer name="slTime" xr10:uid="{F4CD45CC-DCC4-4633-9C2E-C14D8F3CD2C4}" cache="Slicer_Time_block_this_submission_covers" caption="Time block" rowHeight="241300"/>
+  <slicer name="slCampus" xr10:uid="{A2BD6118-9125-49ED-BE5E-8DE8BE07C2FF}" cache="Slicer_Campus" caption="Campus" rowHeight="241300"/>
+  <slicer name="slTime" xr10:uid="{C90CEBF5-B54F-4A33-85BA-F3E0EAF0C8A8}" cache="Slicer_Time_block_this_submission_covers" caption="Time block" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -4680,7 +4680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53BCE8E1-B6A4-44F5-AFF9-2CFE7C6765B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00F2CA1-1639-44F6-ACB5-3F1549586F01}">
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
